--- a/data sample/DATA SAMPLE THANG/2. BÁO CÁO FBB_BAO.xlsx
+++ b/data sample/DATA SAMPLE THANG/2. BÁO CÁO FBB_BAO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\quyng\Documents\TOOL TỔNG HỢP BÁO CÁO\BÁO CÁO TUẦN 29\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\quyng\Documents\TOOL TỔNG HỢP BÁO CÁO\VNPT REPORT\data sample\DATA SAMPLE THANG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AC15A6-A9B2-4BB2-8E93-4DD16185F415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6D0020-D719-4FD4-9AB0-F880DBBC1610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="230">
   <si>
     <t>TT</t>
   </si>
@@ -707,6 +707,27 @@
   </si>
   <si>
     <t>99.26</t>
+  </si>
+  <si>
+    <t>B11_BAO</t>
+  </si>
+  <si>
+    <t>B16_BAO</t>
+  </si>
+  <si>
+    <t>B17_BAO</t>
+  </si>
+  <si>
+    <t>B18_BAO</t>
+  </si>
+  <si>
+    <t>B19_BAO</t>
+  </si>
+  <si>
+    <t>B20_BAO</t>
+  </si>
+  <si>
+    <t>B21_BAO</t>
   </si>
 </sst>
 </file>
@@ -905,7 +926,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -967,11 +988,158 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="66">
+  <dxfs count="67">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF27AE60"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5F5E3"/>
+          <bgColor rgb="FFD5F5E3"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1008,9 +1176,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1090,25 +1255,6 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
           <color indexed="64"/>
@@ -1200,15 +1346,15 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FF27AE60"/>
+        <color rgb="FFC0392B"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD5F5E3"/>
-          <bgColor rgb="FFD5F5E3"/>
+          <fgColor rgb="FFFADBD8"/>
+          <bgColor rgb="FFFADBD8"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1268,6 +1414,63 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
           <color indexed="64"/>
@@ -1311,6 +1514,9 @@
           <color indexed="64"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1348,9 +1554,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1494,6 +1697,9 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1783,37 +1989,102 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFC0392B"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFADBD8"/>
-          <bgColor rgb="FFFADBD8"/>
-        </patternFill>
-      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1844,7 +2115,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1863,64 +2133,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -1945,13 +2157,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1961,6 +2166,13 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -2001,178 +2213,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2187,9 +2227,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C5A40A8C-57AA-44BB-97E1-079A579ACAA9}" name="b1_bao" displayName="b1_bao" ref="A1:H17" totalsRowShown="0" headerRowDxfId="54" headerRowBorderDxfId="64" tableBorderDxfId="65" totalsRowBorderDxfId="63">
-  <autoFilter ref="A1:H17" xr:uid="{C5A40A8C-57AA-44BB-97E1-079A579ACAA9}"/>
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C5A40A8C-57AA-44BB-97E1-079A579ACAA9}" name="b1_bao" displayName="b1_bao" ref="A1:I17" totalsRowShown="0" headerRowDxfId="66" headerRowBorderDxfId="65" tableBorderDxfId="64" totalsRowBorderDxfId="63">
+  <autoFilter ref="A1:I17" xr:uid="{C5A40A8C-57AA-44BB-97E1-079A579ACAA9}"/>
+  <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{BBDE7193-E008-43EE-9025-29FDBCBDA645}" name="TT" dataDxfId="62"/>
     <tableColumn id="2" xr3:uid="{CD29724E-C2AC-4C74-97CF-C9399FA2AFD7}" name="Chỉ số" dataDxfId="61"/>
     <tableColumn id="3" xr3:uid="{241C05FC-AB1A-43A7-A104-B74737B3E929}" name="Thành phần" dataDxfId="60"/>
@@ -2198,87 +2238,88 @@
     <tableColumn id="6" xr3:uid="{05612346-5BC8-42EE-832A-12F19A323250}" name="Điểm tổng" dataDxfId="57"/>
     <tableColumn id="7" xr3:uid="{859855CF-95EE-4351-8E78-C40137CA0CEC}" name="Đánh giá" dataDxfId="56"/>
     <tableColumn id="8" xr3:uid="{2E9F4A95-5F04-42B1-AE92-B7302442B0C6}" name="Ghi chú (Mục tiêu/Trọng số)" dataDxfId="55"/>
+    <tableColumn id="9" xr3:uid="{E0859839-D90E-443F-A189-926B5FAB63A4}" name="B11_BAO" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2E36B7EF-773B-458F-A22B-2E72F1D5B41A}" name="b2_bao" displayName="b2_bao" ref="A2:G25" totalsRowShown="0" headerRowDxfId="42" dataDxfId="43" headerRowBorderDxfId="52" tableBorderDxfId="53" totalsRowBorderDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2E36B7EF-773B-458F-A22B-2E72F1D5B41A}" name="b2_bao" displayName="b2_bao" ref="A2:G25" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28" headerRowBorderDxfId="26" tableBorderDxfId="27" totalsRowBorderDxfId="25">
   <autoFilter ref="A2:G25" xr:uid="{2E36B7EF-773B-458F-A22B-2E72F1D5B41A}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{159A8610-ECB8-45DC-8A1D-4F39EF054949}" name="STT" dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{9BFBA7EF-1613-4E68-BCF5-918CA3BAB9FB}" name="THT" dataDxfId="49"/>
-    <tableColumn id="3" xr3:uid="{7CF1089E-96E4-415D-963F-5958FCB7BE34}" name="TTVT" dataDxfId="48"/>
-    <tableColumn id="4" xr3:uid="{3714728C-8CA8-4FA6-9A40-0280E9AF92EA}" name="Thuê bao suy hao" dataDxfId="47"/>
-    <tableColumn id="5" xr3:uid="{7336BE5F-4A74-464C-8EAC-0174ADDEB545}" name="Tỉ lệ suy hao (%)" dataDxfId="46"/>
-    <tableColumn id="6" xr3:uid="{3C42719A-3E06-4739-B5EA-8FB6AF82BCDF}" name="Mục tiêu (%)" dataDxfId="45"/>
-    <tableColumn id="7" xr3:uid="{4397ED06-C235-4032-9BD3-8DF388006130}" name="Đạt/Chưa đạt" dataDxfId="44"/>
+    <tableColumn id="1" xr3:uid="{159A8610-ECB8-45DC-8A1D-4F39EF054949}" name="STT" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{9BFBA7EF-1613-4E68-BCF5-918CA3BAB9FB}" name="THT" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{7CF1089E-96E4-415D-963F-5958FCB7BE34}" name="TTVT" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{3714728C-8CA8-4FA6-9A40-0280E9AF92EA}" name="Thuê bao suy hao" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{7336BE5F-4A74-464C-8EAC-0174ADDEB545}" name="Tỉ lệ suy hao (%)" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{3C42719A-3E06-4739-B5EA-8FB6AF82BCDF}" name="Mục tiêu (%)" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{4397ED06-C235-4032-9BD3-8DF388006130}" name="Đạt/Chưa đạt" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6DF854DF-0972-466B-B6AE-7E0E42BE41F9}" name="b3_bao" displayName="b3_bao" ref="A1:B2" totalsRowShown="0" headerRowDxfId="36" headerRowBorderDxfId="40" tableBorderDxfId="41" totalsRowBorderDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6DF854DF-0972-466B-B6AE-7E0E42BE41F9}" name="b3_bao" displayName="b3_bao" ref="A1:B2" totalsRowShown="0" headerRowDxfId="53" headerRowBorderDxfId="51" tableBorderDxfId="52" totalsRowBorderDxfId="50">
   <autoFilter ref="A1:B2" xr:uid="{6DF854DF-0972-466B-B6AE-7E0E42BE41F9}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{6296248D-6202-4D42-8F18-497CD809B4D3}" name="Nguyên nhân" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{5B3DFF35-A203-4359-B71F-41F40EB411AF}" name="Giải pháp" dataDxfId="37"/>
+    <tableColumn id="1" xr3:uid="{6296248D-6202-4D42-8F18-497CD809B4D3}" name="Nguyên nhân" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{5B3DFF35-A203-4359-B71F-41F40EB411AF}" name="Giải pháp" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{960D4AA6-154A-49B8-9051-ABE95CA64672}" name="b4_bao" displayName="b4_bao" ref="A9:D17" totalsRowShown="0" headerRowDxfId="28" headerRowBorderDxfId="34" tableBorderDxfId="35" totalsRowBorderDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{960D4AA6-154A-49B8-9051-ABE95CA64672}" name="b4_bao" displayName="b4_bao" ref="A9:D17" totalsRowShown="0" headerRowDxfId="47" headerRowBorderDxfId="45" tableBorderDxfId="46" totalsRowBorderDxfId="44">
   <autoFilter ref="A9:D17" xr:uid="{960D4AA6-154A-49B8-9051-ABE95CA64672}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{8A52D176-240F-4285-A2FB-DCE95E1A0BCC}" name="STT" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{4585D98E-3893-4E74-8B85-2E672C74A698}" name="THT" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{51B84A2A-B396-4F20-849B-F8C6EA9BC722}" name="FBB QoS" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{120E139B-3B39-4A96-9DFD-0810219C359C}" name="Đạt/Chưa đạt" dataDxfId="29"/>
+    <tableColumn id="1" xr3:uid="{8A52D176-240F-4285-A2FB-DCE95E1A0BCC}" name="STT" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{4585D98E-3893-4E74-8B85-2E672C74A698}" name="THT" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{51B84A2A-B396-4F20-849B-F8C6EA9BC722}" name="FBB QoS" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{120E139B-3B39-4A96-9DFD-0810219C359C}" name="Đạt/Chưa đạt" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6A7D7D46-B85E-4F38-BFA1-0428E22CDE7F}" name="b5_bao" displayName="b5_bao" ref="A20:E43" totalsRowShown="0" headerRowDxfId="18" dataDxfId="19" headerRowBorderDxfId="26" tableBorderDxfId="27" totalsRowBorderDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{6A7D7D46-B85E-4F38-BFA1-0428E22CDE7F}" name="b5_bao" displayName="b5_bao" ref="A20:E43" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38" headerRowBorderDxfId="36" tableBorderDxfId="37" totalsRowBorderDxfId="35">
   <autoFilter ref="A20:E43" xr:uid="{6A7D7D46-B85E-4F38-BFA1-0428E22CDE7F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F0747429-EC4E-4201-A529-971FD1BA3B0E}" name="STT" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{9D17F814-6A8B-443A-AF14-3A1E36792C6B}" name="THT" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{8073CAF0-BA2D-451C-AC5A-DA85CFB80488}" name="TTVT" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{CD7A236D-48FD-4506-BC13-40F3040D2FCD}" name="FBB QoS" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{83EA8966-427B-4737-9869-428BA387F19C}" name="Đạt/Chưa đạt" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{F0747429-EC4E-4201-A529-971FD1BA3B0E}" name="STT" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{9D17F814-6A8B-443A-AF14-3A1E36792C6B}" name="THT" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{8073CAF0-BA2D-451C-AC5A-DA85CFB80488}" name="TTVT" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{CD7A236D-48FD-4506-BC13-40F3040D2FCD}" name="FBB QoS" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{83EA8966-427B-4737-9869-428BA387F19C}" name="Đạt/Chưa đạt" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B8CDC0D1-014C-4FAC-BD6C-30D0DAC49FB2}" name="b6_bao" displayName="b6_bao" ref="A2:D10" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="16" tableBorderDxfId="17" totalsRowBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{B8CDC0D1-014C-4FAC-BD6C-30D0DAC49FB2}" name="b6_bao" displayName="b6_bao" ref="A2:D10" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="15" tableBorderDxfId="16" totalsRowBorderDxfId="14">
   <autoFilter ref="A2:D10" xr:uid="{B8CDC0D1-014C-4FAC-BD6C-30D0DAC49FB2}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D13ED8CF-A660-4370-9B75-ED84DECE9E93}" name="STT" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{04D6996B-9386-407D-9AF3-5EDDD44F59D6}" name="THT" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{2BC602B3-283F-4004-A4C1-06EF2E86FBB5}" name="FBB QoE" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{714D1623-D643-4A18-9CAC-58085C10902F}" name="Đạt/Chưa đạt" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{D13ED8CF-A660-4370-9B75-ED84DECE9E93}" name="STT" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{04D6996B-9386-407D-9AF3-5EDDD44F59D6}" name="THT" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{2BC602B3-283F-4004-A4C1-06EF2E86FBB5}" name="FBB QoE" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{714D1623-D643-4A18-9CAC-58085C10902F}" name="Đạt/Chưa đạt" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{8999C100-5635-4276-8150-141BE2309C3D}" name="b7_bao" displayName="b7_bao" ref="A13:E36" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{8999C100-5635-4276-8150-141BE2309C3D}" name="b7_bao" displayName="b7_bao" ref="A13:E36" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
   <autoFilter ref="A13:E36" xr:uid="{8999C100-5635-4276-8150-141BE2309C3D}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A00C2A19-4888-4746-AAE2-89C85A5DC138}" name="STT" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{E3356CB7-DCB8-4AAE-8ACE-44AECBE40B56}" name="THT" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{0CDB24CC-049F-467D-837F-E9F3EBE2BEB0}" name="TTVT" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{6637BF5B-E1A5-4716-9741-6AF1F8B35351}" name="FBB QoE" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{D6D7C082-3FE7-4880-9CE7-9D037266BB7E}" name="Đạt/Chưa đạt" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{A00C2A19-4888-4746-AAE2-89C85A5DC138}" name="STT" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{E3356CB7-DCB8-4AAE-8ACE-44AECBE40B56}" name="THT" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{0CDB24CC-049F-467D-837F-E9F3EBE2BEB0}" name="TTVT" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{6637BF5B-E1A5-4716-9741-6AF1F8B35351}" name="FBB QoE" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{D6D7C082-3FE7-4880-9CE7-9D037266BB7E}" name="Đạt/Chưa đạt" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2569,7 +2610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
@@ -2580,7 +2621,7 @@
     <col min="8" max="8" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -2605,8 +2646,11 @@
       <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="13" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>8</v>
       </c>
@@ -2631,8 +2675,9 @@
       <c r="H2" s="10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="25"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
       <c r="B3" s="5"/>
       <c r="C3" s="2" t="s">
@@ -2645,8 +2690,9 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="11"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="9"/>
       <c r="B4" s="5"/>
       <c r="C4" s="2" t="s">
@@ -2659,8 +2705,9 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="11"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="9"/>
       <c r="B5" s="5"/>
       <c r="C5" s="2" t="s">
@@ -2673,8 +2720,9 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="11"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" s="5"/>
       <c r="C6" s="2" t="s">
@@ -2687,8 +2735,9 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="11"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
       <c r="B7" s="5"/>
       <c r="C7" s="2" t="s">
@@ -2701,8 +2750,9 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="11"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>23</v>
       </c>
@@ -2727,8 +2777,9 @@
       <c r="H8" s="10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="B9" s="5"/>
       <c r="C9" s="2" t="s">
@@ -2741,8 +2792,9 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="11"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I9" s="5"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
       <c r="B10" s="5"/>
       <c r="C10" s="2" t="s">
@@ -2755,8 +2807,9 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="11"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" s="5"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="5"/>
       <c r="C11" s="2" t="s">
@@ -2769,8 +2822,9 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="11"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="5"/>
       <c r="C12" s="2" t="s">
@@ -2783,8 +2837,9 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="11"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="5"/>
       <c r="C13" s="2" t="s">
@@ -2797,8 +2852,9 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="11"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="5"/>
       <c r="C14" s="2" t="s">
@@ -2811,8 +2867,9 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="11"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="5"/>
       <c r="C15" s="2" t="s">
@@ -2825,8 +2882,9 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="11"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="5"/>
       <c r="C16" s="2" t="s">
@@ -2839,8 +2897,9 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="11"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="15"/>
       <c r="B17" s="16"/>
       <c r="C17" s="17" t="s">
@@ -2853,6 +2912,7 @@
       <c r="F17" s="16"/>
       <c r="G17" s="16"/>
       <c r="H17" s="18"/>
+      <c r="I17" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2864,7 +2924,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:G25"/>
+  <dimension ref="A2:H25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
@@ -2876,7 +2936,7 @@
     <col min="7" max="7" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>61</v>
       </c>
@@ -2899,7 +2959,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>8</v>
       </c>
@@ -2921,8 +2981,11 @@
       <c r="G3" s="19" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>23</v>
       </c>
@@ -2945,7 +3008,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>69</v>
       </c>
@@ -2968,7 +3031,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>72</v>
       </c>
@@ -2991,7 +3054,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>12</v>
       </c>
@@ -3014,7 +3077,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>77</v>
       </c>
@@ -3037,7 +3100,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>80</v>
       </c>
@@ -3060,7 +3123,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>97</v>
       </c>
@@ -3083,7 +3146,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>99</v>
       </c>
@@ -3106,7 +3169,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>102</v>
       </c>
@@ -3129,7 +3192,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>105</v>
       </c>
@@ -3152,7 +3215,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>108</v>
       </c>
@@ -3175,7 +3238,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>111</v>
       </c>
@@ -3198,7 +3261,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>114</v>
       </c>
@@ -3452,6 +3515,9 @@
       <c r="B1" s="14" t="s">
         <v>46</v>
       </c>
+      <c r="C1" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="2" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
@@ -3544,6 +3610,9 @@
       <c r="D10" s="19" t="s">
         <v>66</v>
       </c>
+      <c r="E10" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
@@ -3629,7 +3698,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="15"/>
       <c r="B17" s="17" t="s">
         <v>83</v>
@@ -3641,12 +3710,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>61</v>
       </c>
@@ -3663,7 +3732,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>8</v>
       </c>
@@ -3679,8 +3748,11 @@
       <c r="E21" s="19" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>2</v>
       </c>
@@ -3697,7 +3769,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>69</v>
       </c>
@@ -3714,7 +3786,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>72</v>
       </c>
@@ -3731,7 +3803,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>12</v>
       </c>
@@ -3748,7 +3820,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>77</v>
       </c>
@@ -3765,7 +3837,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>80</v>
       </c>
@@ -3782,7 +3854,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>97</v>
       </c>
@@ -3799,7 +3871,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>99</v>
       </c>
@@ -3816,7 +3888,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>102</v>
       </c>
@@ -3833,7 +3905,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>105</v>
       </c>
@@ -3850,7 +3922,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>108</v>
       </c>
@@ -4062,7 +4134,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -4071,12 +4143,12 @@
     <col min="4" max="5" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>61</v>
       </c>
@@ -4090,7 +4162,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>8</v>
       </c>
@@ -4103,8 +4175,11 @@
       <c r="D3" s="20" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>23</v>
       </c>
@@ -4118,7 +4193,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>69</v>
       </c>
@@ -4132,7 +4207,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>72</v>
       </c>
@@ -4146,7 +4221,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>12</v>
       </c>
@@ -4160,7 +4235,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>77</v>
       </c>
@@ -4174,7 +4249,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>80</v>
       </c>
@@ -4188,7 +4263,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="15"/>
       <c r="B10" s="17" t="s">
         <v>83</v>
@@ -4200,12 +4275,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>61</v>
       </c>
@@ -4222,7 +4297,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>8</v>
       </c>
@@ -4238,8 +4313,11 @@
       <c r="E14" s="20" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>23</v>
       </c>
@@ -4256,7 +4334,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>69</v>
       </c>
